--- a/Result/profitability/2534.xlsx
+++ b/Result/profitability/2534.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>1.07</v>
       </c>
       <c r="M2" t="n">
-        <v>0.4712500000000001</v>
+        <v>0.44875</v>
       </c>
       <c r="N2" t="n">
-        <v>52.80125</v>
+        <v>54.5275</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,16 +780,16 @@
         <v>0.04</v>
       </c>
       <c r="M3" t="n">
-        <v>0.47375</v>
+        <v>0.375</v>
       </c>
       <c r="N3" t="n">
-        <v>51.49874999999999</v>
+        <v>55.4925</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>-0.03</v>
       </c>
       <c r="M4" t="n">
-        <v>0.39125</v>
+        <v>0.245</v>
       </c>
       <c r="N4" t="n">
-        <v>49.48999999999999</v>
+        <v>53.68875</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.02</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2625</v>
+        <v>0.14</v>
       </c>
       <c r="N5" t="n">
-        <v>50.30625</v>
+        <v>54.6725</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.09</v>
       </c>
       <c r="M6" t="n">
-        <v>0.14875</v>
+        <v>0.125</v>
       </c>
       <c r="N6" t="n">
-        <v>51.4825</v>
+        <v>52.78625</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.24</v>
       </c>
       <c r="M7" t="n">
-        <v>0.175</v>
+        <v>0.12875</v>
       </c>
       <c r="N7" t="n">
-        <v>49.84249999999999</v>
+        <v>49.98375</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>0.91</v>
       </c>
       <c r="M8" t="n">
-        <v>0.2625000000000001</v>
+        <v>0.245</v>
       </c>
       <c r="N8" t="n">
-        <v>47.57375</v>
+        <v>47.22624999999999</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -9830,6 +9830,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2534</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>297</v>
+      </c>
+      <c r="D75" t="n">
+        <v>86</v>
+      </c>
+      <c r="E75" t="n">
+        <v>212</v>
+      </c>
+      <c r="F75" t="n">
+        <v>71.20999999999999</v>
+      </c>
+      <c r="G75" t="n">
+        <v>53</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>17.73%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-111</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-58</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-75</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-0.16</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.3175</v>
+      </c>
+      <c r="N75" t="n">
+        <v>55.82749999999999</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.14</v>
+      </c>
+      <c r="X75" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-2.780000000000001</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.03757264495202051</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>-0.98</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-1.195121951219512</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>34.92999999999999</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.9627894156560086</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
